--- a/research/traditional_assets/database/data/barbados/barbados_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/barbados/barbados_green_renewable_energy.xlsx
@@ -594,16 +594,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-4.37037037037037</v>
+        <v>0.874074074074074</v>
       </c>
       <c r="J2">
-        <v>-4.37037037037037</v>
+        <v>0.874074074074074</v>
       </c>
       <c r="K2">
-        <v>-0.158</v>
+        <v>1.18</v>
       </c>
       <c r="L2">
-        <v>-5.851851851851852</v>
+        <v>0.874074074074074</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,37 +621,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.396</v>
+        <v>0.196</v>
       </c>
       <c r="V2">
-        <v>0.02429447852760736</v>
+        <v>0.01689655172413793</v>
       </c>
       <c r="W2">
-        <v>-0.00802030456852792</v>
+        <v>0.06051282051282051</v>
       </c>
       <c r="X2">
-        <v>0.1520581588233532</v>
+        <v>0.2932030080475011</v>
       </c>
       <c r="Y2">
-        <v>-0.1600784633918811</v>
+        <v>-0.2326901875346806</v>
       </c>
       <c r="Z2">
-        <v>0.00141287284144427</v>
+        <v>0.04638537658053876</v>
       </c>
       <c r="AA2">
-        <v>-0.006174777603349032</v>
+        <v>0.04054425508521165</v>
       </c>
       <c r="AB2">
-        <v>0.1272095170014466</v>
+        <v>0.2233260983160297</v>
       </c>
       <c r="AC2">
-        <v>-0.1333842946047956</v>
+        <v>-0.1827818432308181</v>
       </c>
       <c r="AD2">
         <v>10</v>
@@ -663,19 +663,19 @@
         <v>10</v>
       </c>
       <c r="AG2">
-        <v>9.603999999999999</v>
+        <v>9.804</v>
       </c>
       <c r="AH2">
-        <v>0.3802281368821293</v>
+        <v>0.4629629629629629</v>
       </c>
       <c r="AI2">
-        <v>0.3389830508474576</v>
+        <v>0.3257328990228013</v>
       </c>
       <c r="AJ2">
-        <v>0.3707535515750463</v>
+        <v>0.458045225191553</v>
       </c>
       <c r="AK2">
-        <v>0.3299890049477735</v>
+        <v>0.3214004720692368</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,16 +707,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-4.37037037037037</v>
+        <v>0.874074074074074</v>
       </c>
       <c r="J3">
-        <v>-4.37037037037037</v>
+        <v>0.874074074074074</v>
       </c>
       <c r="K3">
-        <v>-0.158</v>
+        <v>1.18</v>
       </c>
       <c r="L3">
-        <v>-5.851851851851852</v>
+        <v>0.874074074074074</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -725,7 +725,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -734,37 +734,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.396</v>
+        <v>0.196</v>
       </c>
       <c r="V3">
-        <v>0.02429447852760736</v>
+        <v>0.01689655172413793</v>
       </c>
       <c r="W3">
-        <v>-0.00802030456852792</v>
+        <v>0.06051282051282051</v>
       </c>
       <c r="X3">
-        <v>0.1520581588233532</v>
+        <v>0.2932030080475011</v>
       </c>
       <c r="Y3">
-        <v>-0.1600784633918811</v>
+        <v>-0.2326901875346806</v>
       </c>
       <c r="Z3">
-        <v>0.00141287284144427</v>
+        <v>0.04638537658053876</v>
       </c>
       <c r="AA3">
-        <v>-0.006174777603349032</v>
+        <v>0.04054425508521165</v>
       </c>
       <c r="AB3">
-        <v>0.1272095170014466</v>
+        <v>0.2233260983160297</v>
       </c>
       <c r="AC3">
-        <v>-0.1333842946047956</v>
+        <v>-0.1827818432308181</v>
       </c>
       <c r="AD3">
         <v>10</v>
@@ -776,19 +776,19 @@
         <v>10</v>
       </c>
       <c r="AG3">
-        <v>9.603999999999999</v>
+        <v>9.804</v>
       </c>
       <c r="AH3">
-        <v>0.3802281368821293</v>
+        <v>0.4629629629629629</v>
       </c>
       <c r="AI3">
-        <v>0.3389830508474576</v>
+        <v>0.3257328990228013</v>
       </c>
       <c r="AJ3">
-        <v>0.3707535515750463</v>
+        <v>0.458045225191553</v>
       </c>
       <c r="AK3">
-        <v>0.3299890049477735</v>
+        <v>0.3214004720692368</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/barbados/barbados_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/barbados/barbados_green_renewable_energy.xlsx
@@ -587,23 +587,8 @@
           <t>Green &amp; Renewable Energy</t>
         </is>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0.874074074074074</v>
-      </c>
-      <c r="J2">
-        <v>0.874074074074074</v>
-      </c>
       <c r="K2">
-        <v>1.18</v>
-      </c>
-      <c r="L2">
-        <v>0.874074074074074</v>
+        <v>-2.21</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,37 +606,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.196</v>
+        <v>0.021</v>
       </c>
       <c r="V2">
-        <v>0.01689655172413793</v>
+        <v>0.00168</v>
       </c>
       <c r="W2">
-        <v>0.06051282051282051</v>
+        <v>-0.1067632850241546</v>
       </c>
       <c r="X2">
-        <v>0.2932030080475011</v>
+        <v>0.1819778949579279</v>
       </c>
       <c r="Y2">
-        <v>-0.2326901875346806</v>
+        <v>-0.2887411799820825</v>
       </c>
       <c r="Z2">
-        <v>0.04638537658053876</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0.04054425508521165</v>
+        <v>-0.07244951481772882</v>
       </c>
       <c r="AB2">
-        <v>0.2233260983160297</v>
+        <v>0.1533185663095191</v>
       </c>
       <c r="AC2">
-        <v>-0.1827818432308181</v>
+        <v>-0.2257680811272479</v>
       </c>
       <c r="AD2">
         <v>10</v>
@@ -663,19 +648,19 @@
         <v>10</v>
       </c>
       <c r="AG2">
-        <v>9.804</v>
+        <v>9.978999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.4629629629629629</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AI2">
-        <v>0.3257328990228013</v>
+        <v>0.3508771929824561</v>
       </c>
       <c r="AJ2">
-        <v>0.458045225191553</v>
+        <v>0.4439254415231994</v>
       </c>
       <c r="AK2">
-        <v>0.3214004720692368</v>
+        <v>0.3503985392745532</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -700,23 +685,8 @@
           <t>Green &amp; Renewable Energy</t>
         </is>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0.874074074074074</v>
-      </c>
-      <c r="J3">
-        <v>0.874074074074074</v>
-      </c>
       <c r="K3">
-        <v>1.18</v>
-      </c>
-      <c r="L3">
-        <v>0.874074074074074</v>
+        <v>-2.21</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -725,7 +695,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -734,37 +704,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.196</v>
+        <v>0.021</v>
       </c>
       <c r="V3">
-        <v>0.01689655172413793</v>
+        <v>0.00168</v>
       </c>
       <c r="W3">
-        <v>0.06051282051282051</v>
+        <v>-0.1067632850241546</v>
       </c>
       <c r="X3">
-        <v>0.2932030080475011</v>
+        <v>0.1819778949579279</v>
       </c>
       <c r="Y3">
-        <v>-0.2326901875346806</v>
+        <v>-0.2887411799820825</v>
       </c>
       <c r="Z3">
-        <v>0.04638537658053876</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.04054425508521165</v>
+        <v>-0.07244951481772882</v>
       </c>
       <c r="AB3">
-        <v>0.2233260983160297</v>
+        <v>0.1533185663095191</v>
       </c>
       <c r="AC3">
-        <v>-0.1827818432308181</v>
+        <v>-0.2257680811272479</v>
       </c>
       <c r="AD3">
         <v>10</v>
@@ -776,19 +746,19 @@
         <v>10</v>
       </c>
       <c r="AG3">
-        <v>9.804</v>
+        <v>9.978999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.4629629629629629</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="AI3">
-        <v>0.3257328990228013</v>
+        <v>0.3508771929824561</v>
       </c>
       <c r="AJ3">
-        <v>0.458045225191553</v>
+        <v>0.4439254415231994</v>
       </c>
       <c r="AK3">
-        <v>0.3214004720692368</v>
+        <v>0.3503985392745532</v>
       </c>
       <c r="AL3">
         <v>0</v>
